--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3E9DC95-95C2-47C5-BB85-060DF0B16853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D31D478-0670-472A-B2CE-FCC19CF66425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="165" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -127,6 +127,14 @@
   </si>
   <si>
     <t>0.0,98.0,0.0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフセット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0.0,0.0,0.0</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -521,8 +529,8 @@
       <c r="D2" s="1">
         <v>80</v>
       </c>
-      <c r="E2" s="1">
-        <v>-1</v>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>-1</v>
@@ -533,7 +541,7 @@
       </c>
       <c r="H2" s="1" t="str">
         <f>VLOOKUP(Sheet1!C:C,Reference!B:F,4,FALSE)</f>
-        <v>未使用</v>
+        <v>オフセット</v>
       </c>
       <c r="I2" s="1" t="str">
         <f>VLOOKUP(Sheet1!C:C,Reference!B:F,5,FALSE)</f>
@@ -663,7 +671,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>

--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D31D478-0670-472A-B2CE-FCC19CF66425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A1D3FF-2A04-4BD7-9363-D3ACF8E444A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="165" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -130,11 +130,75 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>オフセット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>0.0,0.0,0.0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーと地形の当たり判定</t>
+    <rPh sb="6" eb="8">
+      <t>チケイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドラゴンと地形の当たり判定</t>
+    <rPh sb="5" eb="7">
+      <t>チケイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復アイテム本体の当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復アイテムのエフェクトの当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>継続ダメージアイテムのエフェクトの当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンテイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -477,146 +541,268 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1">
-        <v>0</v>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <f>VLOOKUP(B2,Reference!A:B,2,FALSE)</f>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>VLOOKUP(C2,Reference!A:B,2,FALSE)</f>
+        <v>AABB</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
+        <v>各軸の大きさ</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
+        <v>オフセット座標</v>
+      </c>
+      <c r="J2" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>VLOOKUP(C3,Reference!A:B,2,FALSE)</f>
+        <v>AABB</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
+        <v>各軸の大きさ</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
+        <v>オフセット座標</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1">
+        <v>100</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>VLOOKUP(C4,Reference!A:B,2,FALSE)</f>
         <v>Sphere</v>
       </c>
-      <c r="D2" s="1">
-        <v>80</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E4" s="1">
+        <v>420</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1">
         <v>-1</v>
       </c>
-      <c r="G2" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,3,FALSE)</f>
+      <c r="H4" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
         <v>半径</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,4,FALSE)</f>
-        <v>オフセット</v>
-      </c>
-      <c r="I2" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,5,FALSE)</f>
+      <c r="I4" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
+        <v>オフセット座標</v>
+      </c>
+      <c r="J4" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="str">
-        <f>VLOOKUP(B3,Reference!A:B,2,FALSE)</f>
-        <v>AABB</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1">
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1">
+        <v>101</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>VLOOKUP(C5,Reference!A:B,2,FALSE)</f>
+        <v>Sphere</v>
+      </c>
+      <c r="E5" s="1">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1">
         <v>-1</v>
       </c>
-      <c r="G3" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,3,FALSE)</f>
+      <c r="H5" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
+      <c r="I5" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="H3" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,4,FALSE)</f>
-        <v>各軸の大きさ</v>
-      </c>
-      <c r="I3" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,5,FALSE)</f>
+      <c r="J5" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="str">
-        <f>VLOOKUP(B4,Reference!A:B,2,FALSE)</f>
-        <v>AABB</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1">
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
+        <v>110</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>VLOOKUP(C6,Reference!A:B,2,FALSE)</f>
+        <v>Sphere</v>
+      </c>
+      <c r="E6" s="1">
+        <v>300</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
         <v>-1</v>
       </c>
-      <c r="G4" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,3,FALSE)</f>
+      <c r="H6" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
+      <c r="I6" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,4,FALSE)</f>
-        <v>各軸の大きさ</v>
-      </c>
-      <c r="I4" s="1" t="str">
-        <f>VLOOKUP(Sheet1!C:C,Reference!B:F,5,FALSE)</f>
+      <c r="J6" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1">
+        <v>111</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>VLOOKUP(C7,Reference!A:B,2,FALSE)</f>
+        <v>Sphere</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
+        <v>オフセット座標</v>
+      </c>
+      <c r="J7" s="1" t="str">
+        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -624,7 +810,7 @@
           <x14:formula1>
             <xm:f>Reference!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B4</xm:sqref>
+          <xm:sqref>C2:C7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -639,8 +825,7 @@
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -671,7 +856,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -685,10 +870,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -697,5 +882,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A1D3FF-2A04-4BD7-9363-D3ACF8E444A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09927590-3428-4DDC-8FA7-299812872CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="-13365" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -197,6 +197,22 @@
       <t>ア</t>
     </rPh>
     <rPh sb="20" eb="22">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>継続ダメージアイテム本体の当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="16" eb="18">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -657,7 +673,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1">
         <v>100</v>
@@ -670,7 +686,7 @@
         <v>Sphere</v>
       </c>
       <c r="E4" s="1">
-        <v>420</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
@@ -693,7 +709,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1">
         <v>101</v>
@@ -706,7 +722,7 @@
         <v>Sphere</v>
       </c>
       <c r="E5" s="1">
-        <v>30</v>
+        <v>420</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
@@ -729,10 +745,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -742,7 +758,7 @@
         <v>Sphere</v>
       </c>
       <c r="E6" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -768,7 +784,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="1">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -778,7 +794,7 @@
         <v>Sphere</v>
       </c>
       <c r="E7" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -810,7 +826,7 @@
           <x14:formula1>
             <xm:f>Reference!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C7</xm:sqref>
+          <xm:sqref>C2:C5 C6:C7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09927590-3428-4DDC-8FA7-299812872CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361184FC-1B5C-4C3A-988F-5895C647005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="-13365" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6210" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -160,59 +160,62 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>回復アイテム本体の当たり判定</t>
+    <t>回復瓶S本体の当たり判定</t>
     <rPh sb="0" eb="2">
       <t>カイフク</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh sb="2" eb="3">
+      <t>ビン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
       <t>ホンタイ</t>
     </rPh>
-    <rPh sb="9" eb="10">
+    <rPh sb="7" eb="8">
       <t>ア</t>
     </rPh>
-    <rPh sb="12" eb="14">
+    <rPh sb="10" eb="12">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>回復アイテムのエフェクトの当たり判定</t>
+    <t>回復瓶Sのエフェクトの当たり判定</t>
     <rPh sb="0" eb="2">
       <t>カイフク</t>
     </rPh>
-    <rPh sb="13" eb="14">
+    <rPh sb="11" eb="12">
       <t>ア</t>
     </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="14" eb="16">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>継続ダメージアイテムのエフェクトの当たり判定</t>
-    <rPh sb="0" eb="2">
-      <t>ケイゾク</t>
-    </rPh>
-    <rPh sb="17" eb="18">
+    <t>火炎瓶S本体の当たり判定</t>
+    <rPh sb="0" eb="3">
+      <t>カエンビン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
       <t>ア</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="9" eb="11">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>継続ダメージアイテム本体の当たり判定</t>
-    <rPh sb="0" eb="2">
-      <t>ケイゾク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホンタイ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
+    <t>火炎瓶Sのエフェクトの当たり判定</t>
+    <rPh sb="0" eb="3">
+      <t>カエンビン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
       <t>ア</t>
     </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="14" eb="16">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -560,7 +563,8 @@
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
@@ -569,10 +573,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -600,11 +604,11 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -636,11 +640,11 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="1">
-        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -672,11 +676,11 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1">
+        <v>100</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" s="1">
-        <v>100</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -708,11 +712,11 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="1">
+        <v>101</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="1">
-        <v>101</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -744,11 +748,11 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="1">
-        <v>210</v>
+      <c r="A6" s="1">
+        <v>200</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -780,11 +784,11 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="1">
-        <v>211</v>
+      <c r="A7" s="1">
+        <v>201</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
